--- a/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
+++ b/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
@@ -902,7 +902,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
+    <row r="18" ht="63" customHeight="1">
       <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -910,11 +910,11 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Tasks 9 and 10 and bonus parts B1–B3 use TEXTBEFORE, TEXTAFTER, or TEXTSPLIT, which need Microsoft 365, Excel for the web, or Excel 2024. In older versions those functions show #NAME?, so use the classic LEFT, MID, and FIND methods from the guide instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33" customHeight="1">
+          <t>Tasks 9 and 10 and bonus parts B1–B3 use TEXTBEFORE, TEXTAFTER, or TEXTSPLIT, which need Microsoft 365, Excel for the web, or Excel 2024. In older versions those functions show #NAME?, so use the classic LEFT, MID, and FIND methods from the guide instead. Task 11 uses TEXTJOIN, which needs Excel 2019 or later. In Excel 2016, join the pieces with &amp; and an IF instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -922,7 +922,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Tasks 2, 8, 11, and 12 ask you to fill a yellow column on a data sheet. The data sheets are Excel Tables, so a formula typed in the first row usually fills the whole column automatically.</t>
+          <t>Tasks 2, 8, 11, and 12 and bonus parts B1, B2, and B4 ask you to fill a yellow column on a data sheet. The data sheets are Excel Tables, so a formula typed in the first row usually fills the whole column automatically.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>TEXTBEFORE (Microsoft 365), or LEFT + FIND</t>
+          <t>TEXTBEFORE (Microsoft 365 or Excel 2024), or LEFT + FIND</t>
         </is>
       </c>
       <c r="D14" s="21" t="n"/>
@@ -26317,7 +26317,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>The city is everything before the second-to-last space. TEXTBEFORE accepts a negative instance_num</t>
+          <t>The city is everything before the second-to-last space. TEXTBEFORE accepts a negative instance_num.</t>
         </is>
       </c>
       <c r="D6" cm="1" s="23">
@@ -39237,7 +39237,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>TEXTJOIN puts the delimiter between items. With ignore_empty set to TRUE, it skips the blank email, so those rows show only the phone. With FALSE, or with D2&amp;" | "&amp;E2, every row gets a separator and the blank rows end in a dangling " | ".</t>
+          <t>TEXTJOIN puts the delimiter between items. With ignore_empty set to TRUE, it skips the blank email, so those rows show only the phone. With FALSE, or with D2&amp;" | "&amp;E2, every row gets a separator and the blank rows end in a dangling " | ". Without TEXTJOIN (Excel 2016), add the separator only when there is an email: =D2&amp;IF(E2="",""," | "&amp;E2).</t>
         </is>
       </c>
     </row>

--- a/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
+++ b/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
@@ -406,9 +406,9 @@
     <tableColumn id="4" name="Phone"/>
     <tableColumn id="5" name="Email"/>
     <tableColumn id="6" name="ChronicConditions"/>
-    <tableColumn id="7" name="FirstName"/>
+    <tableColumn id="7" name="HasDM"/>
     <tableColumn id="8" name="ContactLine"/>
-    <tableColumn id="9" name="HasDM"/>
+    <tableColumn id="9" name="FirstName"/>
     <tableColumn id="10" name="ConditionCount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
@@ -1092,10 +1092,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Tasks use the Patients, Encounters, and Providers sheets. When a task names one patient, it also gives the row, so you can point your formula at that row's cells (for example Patients!C25). Column tasks ask you to fill a yellow column on a data sheet; a gray cell here then summarizes your column.</t>
+          <t>Tasks use the Patients, Encounters, and Providers sheets. When a task names one patient, it also gives the row, so you can point your formula at that row's cells (for example Patients!C25). Column tasks ask you to fill a yellow column on a data sheet, and a gray cell on this sheet then summarizes your column.</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>FIND gives the comma's position; LEFT takes everything before it</t>
+          <t>FIND gives the comma's position, and LEFT takes everything before it</t>
         </is>
       </c>
       <c r="D8" s="21" t="n"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>The appointment-reminder system needs phone numbers as 10 digits with no punctuation. Convert patient PT10058's phone (row 59, "(555) 529-7071") to digits only.</t>
+          <t>The appointment-reminder system needs phone numbers as 10 digits with no punctuation. Convert patient PT10058's phone (row 59 of the Patients sheet, "(555) 529-7071") to digits only.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Patient PT10002's MRN (row 3) shows 897724 because the export stored it as a number and dropped the leading zeros. Return it as the 8-character text MRN printed on wristbands.</t>
+          <t>Patient PT10248's MRN (row 249 of the Patients sheet) shows 57585 because the export stored it as a number and dropped the leading zeros. Return it as the 8-character text MRN printed on wristbands.</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Monthly quality reports label encounters by month. Return the admit month of encounter ENC120217 (row 128 of the Encounters sheet) as text in the form Mon-YYYY, for example Jan-2026.</t>
+          <t>Monthly quality reports label encounters by month. Return the admit month of encounter ENC121048 (row 202 of the Encounters sheet) as text in the form Mon-YYYY, for example Jan-2026.</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Join pieces with &amp;; spaces and punctuation go inside quotes</t>
+          <t>Join the pieces with &amp;. Spaces and punctuation go inside double quotes</t>
         </is>
       </c>
       <c r="D12" s="21" t="n"/>
@@ -1296,7 +1296,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="66" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -1304,16 +1304,16 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>On the Patients sheet, fill the yellow HasDM column with TRUE when the patient's ChronicConditions list includes DM (diabetes) and FALSE otherwise. Blank lists should give FALSE. The gray cell counts the TRUEs.</t>
+          <t>On the Patients sheet, fill the yellow HasDM column with TRUE when the patient's ChronicConditions list includes DM (diabetes) and FALSE otherwise. Blank lists should give FALSE. Type your formula in G2, then copy it down. The gray cell counts the TRUEs.</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>SEARCH returns a position or #VALUE!; ISNUMBER turns that into TRUE/FALSE</t>
+          <t>SEARCH returns a position or #VALUE!, and ISNUMBER turns that into TRUE or FALSE</t>
         </is>
       </c>
       <c r="D13" cm="1" s="23">
-        <f t="array" ref="D13">IF(COUNTA(Patients!I2:I401)=0,"",COUNTIF(Patients!I2:I401,TRUE))</f>
+        <f t="array" ref="D13">IF(COUNTA(Patients!G2:G401)=0,"",COUNTIF(Patients!G2:G401,TRUE))</f>
         <v/>
       </c>
       <c r="E13" s="22">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>The patient portal username is the part of the email address before the @. Return the username for patient PT10123 (row 124).</t>
+          <t>The patient portal username is the part of the email address before the @. Return the username for patient PT10123 (row 124 of the Patients sheet).</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1343,7 +1343,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="66" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>10</t>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>How many chronic conditions does patient PT10101 (row 102) have? Split the semicolon-separated ChronicConditions list with TEXTSPLIT and count the pieces.</t>
+          <t>How many chronic conditions does patient PT10101 (row 102 of the Patients sheet) have? Split the semicolon-separated ChronicConditions list with TEXTSPLIT and count the pieces.</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>COUNTA(TEXTSPLIT(…)) returns one number instead of a spill</t>
+          <t>COUNTA(TEXTSPLIT(…)) returns one number instead of a spill. Without TEXTSPLIT, count the semicolons with LEN and SUBSTITUTE (guide section 6)</t>
         </is>
       </c>
       <c r="D15" s="24" t="n"/>
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="66" customHeight="1">
+    <row r="16" ht="81" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>11</t>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>On the Patients sheet, fill the yellow ContactLine column with the phone and email joined by " | " (space, vertical bar, space), for example (555) 875-0698 | edward.abbott94@example.com. When there's no email, show just the phone, with no dangling separator. The gray cell counts lines that contain a |.</t>
+          <t>On the Patients sheet, fill the yellow ContactLine column with the phone and email joined by " | " (space, vertical bar, space), for example (555) 875-0698 | edward.abbott94@example.com. When there's no email, show just the phone, with no dangling delimiter. Type your formula in H2, then copy it down. The gray cell counts lines that contain a |.</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -1390,7 +1390,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="96" customHeight="1">
+    <row r="17" ht="111" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>12</t>
@@ -1398,16 +1398,16 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>On the Patients sheet, fill the yellow FirstName column with each patient's first name: everything after the comma in PatientName, with no extra spaces. Watch out: some names have doubled, leading, or trailing spaces, and 28 were pasted from the patient portal with non-breaking spaces (UNICHAR(160)). Case doesn't matter here. The gray cell adds up the lengths of all your first names, so any leftover space changes the total.</t>
+          <t>On the Patients sheet, fill the yellow FirstName column with each patient's first name: everything after the comma in PatientName, with no extra spaces. Watch out: some names have doubled, leading, or trailing spaces, and 28 were pasted from the patient portal with non-breaking spaces (UNICHAR(160)). Case doesn't matter here. Type your formula in I2, then copy it down. The gray cell adds up the lengths of all your first names, so any leftover space changes the total.</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>TRIM can't remove a non-breaking space; SUBSTITUTE it with a normal space first</t>
+          <t>TRIM can't remove a non-breaking space, so SUBSTITUTE it with a normal space first</t>
         </is>
       </c>
       <c r="D17" cm="1" s="23">
-        <f t="array" ref="D17">IF(COUNTA(Patients!G2:G401)=0,"",SUMPRODUCT(LEN(Patients!G2:G401)))</f>
+        <f t="array" ref="D17">IF(COUNTA(Patients!I2:I401)=0,"",SUMPRODUCT(LEN(Patients!I2:I401)))</f>
         <v/>
       </c>
       <c r="E17" s="22">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Patient PT10325's name was typed as "o'brien,hannah  " (row 326, with two trailing spaces). Return a clean display name in the form First Last, in Proper Case. This check is case-sensitive.</t>
+          <t>Patient PT10325's name was typed as "o'brien,hannah  " (row 326 of the Patients sheet, with two trailing spaces). Return a clean display name in the form First Last, in Proper Case. This check is case-sensitive.</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -1471,9 +1471,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1510,17 +1510,17 @@
       </c>
       <c r="G1" s="26" t="inlineStr">
         <is>
+          <t>HasDM</t>
+        </is>
+      </c>
+      <c r="H1" s="26" t="inlineStr">
+        <is>
+          <t>ContactLine</t>
+        </is>
+      </c>
+      <c r="I1" s="26" t="inlineStr">
+        <is>
           <t>FirstName</t>
-        </is>
-      </c>
-      <c r="H1" s="26" t="inlineStr">
-        <is>
-          <t>ContactLine</t>
-        </is>
-      </c>
-      <c r="I1" s="26" t="inlineStr">
-        <is>
-          <t>HasDM</t>
         </is>
       </c>
       <c r="J1" s="26" t="inlineStr">
@@ -26304,7 +26304,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="66" customHeight="1">
+    <row r="6" ht="81" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>B1</t>
@@ -26312,7 +26312,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>On the Registrations sheet, fill the yellow City column with just the city name in Proper Case, with no comma, state, or ZIP (for example Lakeview Heights). The gray cell counts rows whose City is exactly Lakeview Heights (case-sensitive). That town appears in every messy style, so it's a good test.</t>
+          <t>On the Registrations sheet, fill the yellow City column with just the city name in Proper Case, with no comma, state, or ZIP (for example Lakeview Heights). Type your formula in D2, then copy it down. The gray cell counts rows whose City is exactly Lakeview Heights (case-sensitive). That town appears in every messy style, so it's a good test.</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -26329,7 +26329,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>B2</t>
@@ -26337,12 +26337,12 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Fill the yellow ZIP5 column with the 5-digit ZIP code as text. ZIP+4 codes like 45720-1280 must become 45720. The gray cell counts rows in ZIP 45501 (downtown Bluestone).</t>
+          <t>On the Registrations sheet, fill the yellow ZIP5 column with the 5-digit ZIP code as text. ZIP+4 codes like 45720-1280 must become 45720. Type your formula in E2, then copy it down. The gray cell counts rows in ZIP 45501 (downtown Bluestone).</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>The ZIP is the last word; keep only its first 5 characters</t>
+          <t>The ZIP is the last word. Keep only its first 5 characters</t>
         </is>
       </c>
       <c r="D7" cm="1" s="23">
@@ -26362,7 +26362,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Write one formula that turns record R1002's CityStateZip (row 3, "CEDAR RIDGE, OH 45720") into the mailing-label line City, ST 12345: city in Proper Case, a comma and a space, the 2-letter state in capitals, a space, and the 5-digit ZIP. This check is case-sensitive.</t>
+          <t>Write one formula that turns record R1002's CityStateZip (row 3 of the Registrations sheet, "CEDAR RIDGE, OH 45720") into the mailing-label line City, ST 12345: city in Proper Case, a comma and a space, the 2-letter state in capitals, a space, and the 5-digit ZIP. This check is case-sensitive.</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -26384,7 +26384,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Back on the Patients sheet, fill the yellow ConditionCount column with the number of chronic conditions each patient has: 0 when ChronicConditions is blank, 1 for HTN, 2 for HTN;DM, and so on. The gray cell counts 'complex' patients with 3 or more conditions.</t>
+          <t>Back on the Patients sheet, fill the yellow ConditionCount column with the number of chronic conditions each patient has: 0 when ChronicConditions is blank, 1 for HTN, 2 for HTN;DM, and so on. Type your formula in J2, then copy it down. The gray cell counts 'complex' patients with 3 or more conditions.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -26409,7 +26409,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>What is the average number of chronic conditions per patient across all 400 patients, including those with none? Use your ConditionCount column. (The check accepts 2 decimal places.)</t>
+          <t>What is the average number of chronic conditions per patient across all 400 patients, including those with none? Use your ConditionCount column. Enter it unrounded or rounded to 2 decimal places. The check accepts either.</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -39007,7 +39007,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>The appointment-reminder system needs phone numbers as 10 digits with no punctuation. Convert patient PT10058's phone (row 59, "(555) 529-7071") to digits only.</t>
+          <t>The appointment-reminder system needs phone numbers as 10 digits with no punctuation. Convert patient PT10058's phone (row 59 of the Patients sheet, "(555) 529-7071") to digits only.</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
@@ -39038,26 +39038,26 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Patient PT10002's MRN (row 3) shows 897724 because the export stored it as a number and dropped the leading zeros. Return it as the 8-character text MRN printed on wristbands.</t>
+          <t>Patient PT10248's MRN (row 249 of the Patients sheet) shows 57585 because the export stored it as a number and dropped the leading zeros. Return it as the 8-character text MRN printed on wristbands.</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>00897724</t>
+          <t>00057585</t>
         </is>
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>=TEXT(Patients!B3,"00000000")</t>
+          <t>=TEXT(Patients!B249,"00000000")</t>
         </is>
       </c>
       <c r="E9" cm="1" s="35">
-        <f t="array" ref="E9">TEXT(Patients!B3,"00000000")</f>
+        <f t="array" ref="E9">TEXT(Patients!B249,"00000000")</f>
         <v/>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>In a format code, each 0 is a required digit, so "00000000" pads the number with leading zeros to 8 digits. The result "00897724" is text, so the zeros are part of the value: they survive joining with &amp; and match MRNs stored as text in other systems. A custom number format (Lesson 1.3) only changes how the cell looks, so ="MRN "&amp;Patients!B3 would still give MRN 897724.</t>
+          <t>In a format code, each 0 is a required digit, so "00000000" pads the number with leading zeros to 8 digits. The result "00057585" is text, so the zeros are part of the value: they survive joining with &amp; and match MRNs stored as text in other systems. A custom number format (Lesson 1.3) only changes how the cell looks, so ="MRN "&amp;Patients!B249 would still give MRN 57585.</t>
         </is>
       </c>
     </row>
@@ -39069,26 +39069,26 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Monthly quality reports label encounters by month. Return the admit month of encounter ENC120217 (row 128 of the Encounters sheet) as text in the form Mon-YYYY, for example Jan-2026.</t>
+          <t>Monthly quality reports label encounters by month. Return the admit month of encounter ENC121048 (row 202 of the Encounters sheet) as text in the form Mon-YYYY, for example Jan-2026.</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>Nov-2025</t>
+          <t>Dec-2025</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>=TEXT(Encounters!D128,"mmm-yyyy")</t>
+          <t>=TEXT(Encounters!D202,"mmm-yyyy")</t>
         </is>
       </c>
       <c r="E10" cm="1" s="35">
-        <f t="array" ref="E10">TEXT(Encounters!D128,"mmm-yyyy")</f>
+        <f t="array" ref="E10">TEXT(Encounters!D202,"mmm-yyyy")</f>
         <v/>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>In a date format code, mmm is the short month name and yyyy is the 4-digit year. The dash is copied as-is. Without TEXT, a date joined to text shows its serial number: ="Admitted "&amp;Encounters!D128 gives Admitted 45975, because a date is stored as a number.</t>
+          <t>In a date format code, mmm is the short month name and yyyy is the 4-digit year. The dash is copied as-is. Without TEXT, a date joined to text shows its serial number: ="Admitted "&amp;Encounters!D202 gives Admitted 46000, because a date is stored as a number.</t>
         </is>
       </c>
     </row>
@@ -39131,7 +39131,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>On the Patients sheet, fill the yellow HasDM column with TRUE when the patient's ChronicConditions list includes DM (diabetes) and FALSE otherwise. Blank lists should give FALSE. The gray cell counts the TRUEs.</t>
+          <t>On the Patients sheet, fill the yellow HasDM column with TRUE when the patient's ChronicConditions list includes DM (diabetes) and FALSE otherwise. Blank lists should give FALSE. Type your formula in G2, then copy it down. The gray cell counts the TRUEs.</t>
         </is>
       </c>
       <c r="C12" s="33" t="n">
@@ -39152,7 +39152,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="96" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>The patient portal username is the part of the email address before the @. Return the username for patient PT10123 (row 124).</t>
+          <t>The patient portal username is the part of the email address before the @. Return the username for patient PT10123 (row 124 of the Patients sheet).</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
@@ -39179,7 +39179,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>TEXTBEFORE returns everything before the first @. The classic version, which works in every Excel, is =LEFT(Patients!E124,FIND("@",Patients!E124)-1).</t>
+          <t>TEXTBEFORE returns everything before the first @, however long the username is. The classic version, which works in every Excel, is =LEFT(Patients!E124,FIND("@",Patients!E124)-1): FIND returns the position of the @ (13 here), and -1 stops LEFT just before it, so it keeps the 12 characters of the username.</t>
         </is>
       </c>
     </row>
@@ -39191,7 +39191,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>How many chronic conditions does patient PT10101 (row 102) have? Split the semicolon-separated ChronicConditions list with TEXTSPLIT and count the pieces.</t>
+          <t>How many chronic conditions does patient PT10101 (row 102 of the Patients sheet) have? Split the semicolon-separated ChronicConditions list with TEXTSPLIT and count the pieces.</t>
         </is>
       </c>
       <c r="C14" s="33" t="n">
@@ -39212,7 +39212,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="96" customHeight="1">
+    <row r="15" ht="111" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>11</t>
@@ -39220,7 +39220,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>On the Patients sheet, fill the yellow ContactLine column with the phone and email joined by " | " (space, vertical bar, space), for example (555) 875-0698 | edward.abbott94@example.com. When there's no email, show just the phone, with no dangling separator. The gray cell counts lines that contain a |.</t>
+          <t>On the Patients sheet, fill the yellow ContactLine column with the phone and email joined by " | " (space, vertical bar, space), for example (555) 875-0698 | edward.abbott94@example.com. When there's no email, show just the phone, with no dangling delimiter. Type your formula in H2, then copy it down. The gray cell counts lines that contain a |.</t>
         </is>
       </c>
       <c r="C15" s="33" t="n">
@@ -39237,7 +39237,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>TEXTJOIN puts the delimiter between items. With ignore_empty set to TRUE, it skips the blank email, so those rows show only the phone. With FALSE, or with D2&amp;" | "&amp;E2, every row gets a separator and the blank rows end in a dangling " | ". Without TEXTJOIN (Excel 2016), add the separator only when there is an email: =D2&amp;IF(E2="",""," | "&amp;E2).</t>
+          <t>TEXTJOIN puts the delimiter between items. With ignore_empty set to TRUE, it skips the blank email, so those rows show only the phone. With FALSE, or with D2&amp;" | "&amp;E2, every row gets a delimiter and the blank rows end in a dangling " | ". Without TEXTJOIN (Excel 2016), add the delimiter only when there is an email: =D2&amp;IF(E2="",""," | "&amp;E2).</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39249,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>On the Patients sheet, fill the yellow FirstName column with each patient's first name: everything after the comma in PatientName, with no extra spaces. Watch out: some names have doubled, leading, or trailing spaces, and 28 were pasted from the patient portal with non-breaking spaces (UNICHAR(160)). Case doesn't matter here. The gray cell adds up the lengths of all your first names, so any leftover space changes the total.</t>
+          <t>On the Patients sheet, fill the yellow FirstName column with each patient's first name: everything after the comma in PatientName, with no extra spaces. Watch out: some names have doubled, leading, or trailing spaces, and 28 were pasted from the patient portal with non-breaking spaces (UNICHAR(160)). Case doesn't matter here. Type your formula in I2, then copy it down. The gray cell adds up the lengths of all your first names, so any leftover space changes the total.</t>
         </is>
       </c>
       <c r="C16" s="33" t="n">
@@ -39278,7 +39278,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Patient PT10325's name was typed as "o'brien,hannah  " (row 326, with two trailing spaces). Return a clean display name in the form First Last, in Proper Case. This check is case-sensitive.</t>
+          <t>Patient PT10325's name was typed as "o'brien,hannah  " (row 326 of the Patients sheet, with two trailing spaces). Return a clean display name in the form First Last, in Proper Case. This check is case-sensitive.</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
@@ -39383,7 +39383,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>On the Registrations sheet, fill the yellow City column with just the city name in Proper Case, with no comma, state, or ZIP (for example Lakeview Heights). The gray cell counts rows whose City is exactly Lakeview Heights (case-sensitive). That town appears in every messy style, so it's a good test.</t>
+          <t>On the Registrations sheet, fill the yellow City column with just the city name in Proper Case, with no comma, state, or ZIP (for example Lakeview Heights). Type your formula in D2, then copy it down. The gray cell counts rows whose City is exactly Lakeview Heights (case-sensitive). That town appears in every messy style, so it's a good test.</t>
         </is>
       </c>
       <c r="C5" s="33" t="n">
@@ -39412,7 +39412,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Fill the yellow ZIP5 column with the 5-digit ZIP code as text. ZIP+4 codes like 45720-1280 must become 45720. The gray cell counts rows in ZIP 45501 (downtown Bluestone).</t>
+          <t>On the Registrations sheet, fill the yellow ZIP5 column with the 5-digit ZIP code as text. ZIP+4 codes like 45720-1280 must become 45720. Type your formula in E2, then copy it down. The gray cell counts rows in ZIP 45501 (downtown Bluestone).</t>
         </is>
       </c>
       <c r="C6" s="33" t="n">
@@ -39441,7 +39441,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Write one formula that turns record R1002's CityStateZip (row 3, "CEDAR RIDGE, OH 45720") into the mailing-label line City, ST 12345: city in Proper Case, a comma and a space, the 2-letter state in capitals, a space, and the 5-digit ZIP. This check is case-sensitive.</t>
+          <t>Write one formula that turns record R1002's CityStateZip (row 3 of the Registrations sheet, "CEDAR RIDGE, OH 45720") into the mailing-label line City, ST 12345: city in Proper Case, a comma and a space, the 2-letter state in capitals, a space, and the 5-digit ZIP. This check is case-sensitive.</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
@@ -39473,7 +39473,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Back on the Patients sheet, fill the yellow ConditionCount column with the number of chronic conditions each patient has: 0 when ChronicConditions is blank, 1 for HTN, 2 for HTN;DM, and so on. The gray cell counts 'complex' patients with 3 or more conditions.</t>
+          <t>Back on the Patients sheet, fill the yellow ConditionCount column with the number of chronic conditions each patient has: 0 when ChronicConditions is blank, 1 for HTN, 2 for HTN;DM, and so on. Type your formula in J2, then copy it down. The gray cell counts 'complex' patients with 3 or more conditions.</t>
         </is>
       </c>
       <c r="C8" s="33" t="n">
@@ -39490,7 +39490,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>LEN(F2)-LEN(SUBSTITUTE(F2,";","")) is the number of semicolons, because removing them shortens the text by exactly that many characters. A list always has one more item than separators, so add 1. The IF handles blank lists: without it, a blank cell has 0 semicolons and would count as 1 condition. COUNTA(TEXTSPLIT(F2,";")) has the same problem on blank cells, so it needs the same IF.</t>
+          <t>LEN(F2)-LEN(SUBSTITUTE(F2,";","")) is the number of semicolons, because removing them shortens the text by exactly that many characters. A list always has one more item than delimiters, so add 1. The IF handles blank lists: without it, a blank cell has 0 semicolons and would count as 1 condition. COUNTA(TEXTSPLIT(F2,";")) has the same problem on blank cells, so it needs the same IF.</t>
         </is>
       </c>
     </row>
@@ -39502,7 +39502,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>What is the average number of chronic conditions per patient across all 400 patients, including those with none? Use your ConditionCount column. (The check accepts 2 decimal places.)</t>
+          <t>What is the average number of chronic conditions per patient across all 400 patients, including those with none? Use your ConditionCount column. Enter it unrounded or rounded to 2 decimal places. The check accepts either.</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">

--- a/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
+++ b/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -287,14 +287,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -866,7 +863,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -874,7 +871,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -954,7 +951,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -978,7 +975,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -998,7 +995,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 400 rows — Excel Table 'tblPatients'</t>
+          <t>Data: 400 rows, in the Excel Table 'tblPatients'</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1007,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 283 rows — Excel Table 'tblEncounters'</t>
+          <t>Data: 283 rows, in the Excel Table 'tblEncounters'</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1019,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 147 rows — Excel Table 'tblProviders'</t>
+          <t>Data: 147 rows, in the Excel Table 'tblProviders'</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1031,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 650 rows — Excel Table 'tblRegistrations'</t>
+          <t>Data: 650 rows, in the Excel Table 'tblRegistrations'</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1089,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="49" customHeight="1">
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Tasks use the Patients, Encounters, and Providers sheets. When a task names one patient, it also gives the row, so you can point your formula at that row's cells (for example Patients!C25). Column tasks ask you to fill a yellow column on a data sheet, and a gray cell on this sheet then summarizes your column.</t>
@@ -26257,7 +26254,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="79" customHeight="1">
+    <row r="2" ht="64" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Bluestone is opening a diabetes education clinic in Cedar Ridge. Marketing wants a clean mailing list from the legacy registration export (the Registrations sheet), and care management wants to know how many current patients are 'complex' (three or more chronic conditions). The export crams city, state, and ZIP into one CityStateZip column in several styles: Cedar Ridge, OH 45720 · CEDAR RIDGE, OH 45720 · Cedar Ridge OH 45720 (no comma) · Cedar Ridge, OH 45720-1280 (ZIP+4). Some city names are two words. (The export also has duplicate records. Removing those is a Lesson 3.3 job, so leave them in.)</t>
@@ -38858,7 +38855,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -38872,7 +38869,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -38929,7 +38926,7 @@
           <t>=RIGHT(Patients!D16,4)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="35">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">RIGHT(Patients!D16,4)</f>
         <v/>
       </c>
@@ -38958,7 +38955,7 @@
           <t>=LEFT(E2,3)</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="35">
+      <c r="E6" cm="1" s="19">
         <f t="array" ref="E6">SUMPRODUCT(--(LEFT(Encounters!E2:E284,3)="E11"))</f>
         <v/>
       </c>
@@ -38989,7 +38986,7 @@
           <t>=LEFT(Patients!C32,FIND(",",Patients!C32)-1)</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="35">
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">LEFT(Patients!C32,FIND(",",Patients!C32)-1)</f>
         <v/>
       </c>
@@ -39020,7 +39017,7 @@
           <t>=SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Patients!D59,"(",""),")","")," ",""),"-","")</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="35">
+      <c r="E8" cm="1" s="19">
         <f t="array" ref="E8">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Patients!D59,"(",""),")","")," ",""),"-","")</f>
         <v/>
       </c>
@@ -39051,7 +39048,7 @@
           <t>=TEXT(Patients!B249,"00000000")</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="35">
+      <c r="E9" cm="1" s="19">
         <f t="array" ref="E9">TEXT(Patients!B249,"00000000")</f>
         <v/>
       </c>
@@ -39082,7 +39079,7 @@
           <t>=TEXT(Encounters!D202,"mmm-yyyy")</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="35">
+      <c r="E10" cm="1" s="19">
         <f t="array" ref="E10">TEXT(Encounters!D202,"mmm-yyyy")</f>
         <v/>
       </c>
@@ -39113,7 +39110,7 @@
           <t>="Dr. "&amp;Providers!B55&amp;" "&amp;Providers!C55&amp;", "&amp;Providers!D55</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="35">
+      <c r="E11" cm="1" s="19">
         <f t="array" ref="E11">"Dr. "&amp;Providers!B55&amp;" "&amp;Providers!C55&amp;", "&amp;Providers!D55</f>
         <v/>
       </c>
@@ -39142,7 +39139,7 @@
           <t>=ISNUMBER(SEARCH("DM",F2))</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="35">
+      <c r="E12" cm="1" s="19">
         <f t="array" ref="E12">SUMPRODUCT(--ISNUMBER(SEARCH("DM",Patients!F2:F401)))</f>
         <v/>
       </c>
@@ -39173,7 +39170,7 @@
           <t>=TEXTBEFORE(Patients!E124,"@")</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="35">
+      <c r="E13" cm="1" s="19">
         <f t="array" ref="E13">_xlfn.TEXTBEFORE(Patients!E124,"@")</f>
         <v/>
       </c>
@@ -39202,7 +39199,7 @@
           <t>=COUNTA(TEXTSPLIT(Patients!F102,";"))</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="35">
+      <c r="E14" cm="1" s="19">
         <f t="array" ref="E14">COUNTA(_xlfn.TEXTSPLIT(Patients!F102,";"))</f>
         <v/>
       </c>
@@ -39231,7 +39228,7 @@
           <t>=TEXTJOIN(" | ",TRUE,D2,E2)</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="35">
+      <c r="E15" cm="1" s="19">
         <f t="array" ref="E15">COUNTA(Patients!E2:E401)</f>
         <v/>
       </c>
@@ -39260,7 +39257,7 @@
           <t>=TRIM(MID(SUBSTITUTE(C2,UNICHAR(160)," "),FIND(",",C2)+1,LEN(C2)))</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="35">
+      <c r="E16" cm="1" s="19">
         <f t="array" ref="E16">SUMPRODUCT(LEN(TRIM(MID(SUBSTITUTE(Patients!C2:C401,_xlfn.UNICHAR(160)," "),FIND(",",Patients!C2:C401)+1,LEN(Patients!C2:C401)))))</f>
         <v/>
       </c>
@@ -39325,7 +39322,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -39339,7 +39336,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -39394,7 +39391,7 @@
           <t>=PROPER(TRIM(SUBSTITUTE(TEXTBEFORE(C2," ",-2),",","")))</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="35">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">COUNTIF(Registrations!C2:C651,"Lakeview Heights*")</f>
         <v/>
       </c>
@@ -39423,7 +39420,7 @@
           <t>=LEFT(TEXTAFTER(C2," ",-1),5)</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="35">
+      <c r="E6" cm="1" s="19">
         <f t="array" ref="E6">COUNTIF(Registrations!C2:C651,"* 45501*")</f>
         <v/>
       </c>
@@ -39484,7 +39481,7 @@
           <t>=IF(F2="",0,LEN(F2)-LEN(SUBSTITUTE(F2,";",""))+1)</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="35">
+      <c r="E8" cm="1" s="19">
         <f t="array" ref="E8">SUMPRODUCT((Patients!F2:F401&lt;&gt;"")*((LEN(Patients!F2:F401)-LEN(SUBSTITUTE(Patients!F2:F401,";",""))+1)&gt;=3))</f>
         <v/>
       </c>
@@ -39505,7 +39502,7 @@
           <t>What is the average number of chronic conditions per patient across all 400 patients, including those with none? Use your ConditionCount column. Enter it unrounded or rounded to 2 decimal places. The check accepts either.</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="35" t="n">
         <v>0.875</v>
       </c>
       <c r="D9" s="34" t="inlineStr">
@@ -39513,7 +39510,7 @@
           <t>=AVERAGE(Patients!J2:J401)</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="37">
+      <c r="E9" cm="1" s="36">
         <f t="array" ref="E9">SUMPRODUCT((Patients!F2:F401&lt;&gt;"")*(LEN(Patients!F2:F401)-LEN(SUBSTITUTE(Patients!F2:F401,";",""))+1))/ROWS(Patients!F2:F401)</f>
         <v/>
       </c>

--- a/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
+++ b/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C33"/>
+  <dimension ref="B2:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -771,7 +771,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Beginner → Intermediate  ·  about 50 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Beginner → Intermediate  ·  about 110 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Use modern TEXTBEFORE, TEXTAFTER, and TEXTSPLIT (Microsoft 365)</t>
+          <t>Use modern TEXTBEFORE, TEXTAFTER, and TEXTSPLIT (Microsoft 365 and Excel 2024)</t>
         </is>
       </c>
     </row>
@@ -990,70 +990,94 @@
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Patients</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 400 rows, in the Excel Table 'tblPatients'</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Encounters</t>
+          <t>Patients</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 283 rows, in the Excel Table 'tblEncounters'</t>
+          <t>Data: 400 rows, in the Excel Table 'tblPatients'</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Providers</t>
+          <t>Encounters</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 147 rows, in the Excel Table 'tblProviders'</t>
+          <t>Data: 283 rows, in the Excel Table 'tblEncounters'</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
+          <t>Providers</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Data: 147 rows, in the Excel Table 'tblProviders'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
           <t>Registrations</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Data: 650 rows, in the Excel Table 'tblRegistrations'</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>400 patients from Bluestone's registration system (names, MRNs, phones, emails, chronic-condition flags), their 283 encounters in Q4 2025, the 147-provider roster, and a 650-row legacy registration export with messy addresses.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>400 patients from Bluestone's registration system (names, MRNs, phones, emails, chronic-condition flags), their 283 encounters in Q4 2025, the 147-provider roster, and a 650-row legacy registration export with messy addresses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
+++ b/02-formulas-functions/02-text-functions/2.2-text-functions.xlsx
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C35"/>
+  <dimension ref="B1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,7 @@
     <col width="95" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -775,6 +776,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -831,6 +833,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -851,7 +854,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -859,7 +862,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell. For tasks 2, 8, 11, and 12, fill the yellow column on the Encounters or Patients sheet instead, and the task's gray cell on Practice reads it.</t>
         </is>
       </c>
     </row>
@@ -919,10 +922,11 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Tasks 2, 8, 11, and 12 and bonus parts B1, B2, and B4 ask you to fill a yellow column on a data sheet. The data sheets are Excel Tables, so a formula typed in the first row usually fills the whole column automatically.</t>
-        </is>
-      </c>
-    </row>
+          <t>Bonus parts B1, B2, and B4 also fill a yellow column, on the Registrations or Patients sheet. The data sheets are Excel Tables, so a formula typed in the first row usually fills the whole column automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
@@ -979,6 +983,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
@@ -1038,24 +1043,24 @@
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Registrations</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 650 rows, in the Excel Table 'tblRegistrations'</t>
+          <t>The bonus challenge (5 parts).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Registrations</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>The bonus challenge (5 parts).</t>
+          <t>Data: 650 rows, in the Excel Table 'tblRegistrations' (used only in the bonus)</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1360,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>TEXTBEFORE (Microsoft 365 or Excel 2024), or LEFT + FIND</t>
+          <t>TEXTBEFORE (Microsoft 365 and Excel 2024), or LEFT + FIND</t>
         </is>
       </c>
       <c r="D14" s="21" t="n"/>
@@ -26288,7 +26293,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>Type a formula or value in each yellow cell. For B1, B2, and B4, fill the yellow column on the Registrations or Patients sheet instead, and the gray cell here reads it. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38994,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>3</t>
@@ -39016,7 +39021,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>FIND(",",…) returns the comma's position (7). The last name is the 6 characters before it, so subtract 1. In Microsoft 365 you can also write =TEXTBEFORE(Patients!C32,",").</t>
+          <t>FIND(",",…) returns the comma's position (7). The last name is the 6 characters before it, so subtract 1. In Microsoft 365 and Excel 2024, you can also write =TEXTBEFORE(Patients!C32,",").</t>
         </is>
       </c>
     </row>
@@ -39287,11 +39292,11 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Work from the inside out. SUBSTITUTE turns each non-breaking space into an ordinary space, MID takes everything after the comma (LEN is simply a length that's long enough), and TRIM removes the leading, trailing, and doubled spaces. Without the SUBSTITUTE, the 28 portal rows keep an invisible character and the total comes out 28 too high. On Windows, CHAR(160) is the same character as UNICHAR(160). A Microsoft 365 version is =TRIM(SUBSTITUTE(TEXTAFTER(C2,","),UNICHAR(160)," ")).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="111" customHeight="1">
+          <t>Work from the inside out. SUBSTITUTE turns each non-breaking space into an ordinary space, MID takes everything after the comma (LEN is simply a length that's long enough), and TRIM removes the leading, trailing, and doubled spaces. Without the SUBSTITUTE, the 28 portal rows keep an invisible character and the total comes out 28 too high. On Windows, CHAR(160) is the same character as UNICHAR(160). A version for Microsoft 365 and Excel 2024 is =TRIM(SUBSTITUTE(TEXTAFTER(C2,","),UNICHAR(160)," ")).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="126" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>13</t>
@@ -39319,7 +39324,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>MID + FIND takes the first name and TRIM drops the trailing spaces. LEFT + FIND takes the last name. Join them with a space and wrap the whole thing in PROPER, which capitalizes the first letter of each word and every letter that follows a non-letter. That's why the B after the apostrophe in O'Brien comes out right. In Microsoft 365: =PROPER(TRIM(TEXTAFTER(Patients!C326,","))&amp;" "&amp;TEXTBEFORE(Patients!C326,",")).</t>
+          <t>MID + FIND takes the first name and TRIM drops the trailing spaces. LEFT + FIND takes the last name. Join them with a space and wrap the whole thing in PROPER, which capitalizes the first letter of each word and every letter that follows a non-letter. That's why the B after the apostrophe in O'Brien comes out right. In Microsoft 365 and Excel 2024: =PROPER(TRIM(TEXTAFTER(Patients!C326,","))&amp;" "&amp;TEXTBEFORE(Patients!C326,",")).</t>
         </is>
       </c>
     </row>
@@ -39396,7 +39401,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="186" customHeight="1">
+    <row r="5" ht="201" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>B1</t>
@@ -39421,7 +39426,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>The commas are unreliable, but the spaces are not: the last two spaces always separate the city, the state, and the ZIP. TEXTBEFORE(C2," ",-2) counts spaces from the end, so it returns everything before the second-to-last space ("Cedar Ridge," or "CEDAR RIDGE"). SUBSTITUTE removes a comma if there is one, TRIM tidies up, and PROPER fixes the case. A FIND(",") approach fails with #VALUE! on the rows that have no comma. Without Microsoft 365, the classic trick is =PROPER(SUBSTITUTE(LEFT(C2,LEN(C2)-LEN(TRIM(RIGHT(SUBSTITUTE(C2," ",REPT(" ",100)),100)))-4),",","")): the TRIM(RIGHT(SUBSTITUTE(…))) part pulls out the last word (the ZIP), and LEFT keeps everything except the ZIP and the 4 characters of " OH ".</t>
+          <t>The commas are unreliable, but the spaces are not: the last two spaces always separate the city, the state, and the ZIP. TEXTBEFORE(C2," ",-2) counts spaces from the end, so it returns everything before the second-to-last space ("Cedar Ridge," or "CEDAR RIDGE"). SUBSTITUTE removes a comma if there is one, TRIM tidies up, and PROPER fixes the case. A FIND(",") approach fails with #VALUE! on the rows that have no comma. Without Microsoft 365 or Excel 2024, the classic trick is =PROPER(SUBSTITUTE(LEFT(C2,LEN(C2)-LEN(TRIM(RIGHT(SUBSTITUTE(C2," ",REPT(" ",100)),100)))-4),",","")): the TRIM(RIGHT(SUBSTITUTE(…))) part pulls out the last word (the ZIP), and LEFT keeps everything except the ZIP and the 4 characters of " OH ".</t>
         </is>
       </c>
     </row>
